--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="237">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T12:52:51+00:00</t>
+    <t>2025-02-24T13:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,10 +311,6 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
-</t>
   </si>
   <si>
     <t>IntendedRecipient.typeId.nullFlavor</t>
@@ -1617,7 +1613,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1625,10 +1621,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1726,39 +1722,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1809,7 +1805,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1829,39 +1825,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1912,7 +1908,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1932,39 +1928,39 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1973,49 +1969,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2035,17 +2031,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -2063,11 +2059,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2118,7 +2114,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2138,10 +2134,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2168,7 +2164,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2219,7 +2215,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2239,10 +2235,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2272,7 +2268,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
@@ -2298,7 +2294,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2316,7 +2312,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2336,10 +2332,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2365,7 +2361,7 @@
         <v>95</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2417,7 +2413,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2437,10 +2433,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2538,39 +2534,39 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E15" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K15" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2621,7 +2617,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2641,39 +2637,39 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E16" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2724,7 +2720,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2744,39 +2740,39 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E17" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2788,7 +2784,7 @@
         <v>74</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>74</v>
@@ -2827,7 +2823,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2847,41 +2843,41 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="F18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K18" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2932,7 +2928,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2952,10 +2948,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2978,7 +2974,7 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -3031,7 +3027,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3051,10 +3047,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3077,10 +3073,10 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -3132,7 +3128,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3152,10 +3148,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3178,10 +3174,10 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -3233,7 +3229,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3253,10 +3249,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3279,10 +3275,10 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -3334,7 +3330,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3354,10 +3350,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3380,10 +3376,10 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>149</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -3435,7 +3431,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3455,10 +3451,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3556,10 +3552,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3657,10 +3653,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3750,7 +3746,7 @@
         <v>74</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>74</v>
@@ -3758,10 +3754,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3859,39 +3855,39 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K28" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3942,7 +3938,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3962,39 +3958,39 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E29" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K29" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4045,7 +4041,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4065,39 +4061,39 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K30" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4106,49 +4102,49 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4168,17 +4164,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>75</v>
@@ -4196,11 +4192,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4251,7 +4247,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4271,10 +4267,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4301,7 +4297,7 @@
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4352,7 +4348,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4372,10 +4368,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4409,7 +4405,7 @@
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>74</v>
@@ -4431,25 +4427,25 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4469,10 +4465,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4506,7 +4502,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>74</v>
@@ -4528,25 +4524,25 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4566,10 +4562,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4595,7 +4591,7 @@
         <v>95</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -4647,7 +4643,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4667,10 +4663,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4768,39 +4764,39 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4851,7 +4847,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4871,39 +4867,39 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K38" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4954,7 +4950,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -4974,39 +4970,39 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K39" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5018,7 +5014,7 @@
         <v>74</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>74</v>
@@ -5057,7 +5053,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5077,17 +5073,17 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>80</v>
@@ -5105,11 +5101,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5160,7 +5156,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5180,10 +5176,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5206,10 +5202,10 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -5261,7 +5257,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5281,10 +5277,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5307,10 +5303,10 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -5362,7 +5358,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5382,10 +5378,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5408,10 +5404,10 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -5463,7 +5459,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5483,10 +5479,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5509,10 +5505,10 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -5540,29 +5536,29 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5582,10 +5578,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5683,10 +5679,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5715,7 +5711,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5746,25 +5742,25 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5784,17 +5780,17 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>80</v>
@@ -5812,11 +5808,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5867,7 +5863,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -5887,17 +5883,17 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>80</v>
@@ -5915,11 +5911,11 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5970,7 +5966,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -5990,17 +5986,17 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
@@ -6018,11 +6014,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6073,7 +6069,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6093,17 +6089,17 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
@@ -6121,11 +6117,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6176,7 +6172,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6196,10 +6192,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6222,11 +6218,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6277,7 +6273,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6297,10 +6293,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6323,11 +6319,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6378,7 +6374,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6398,39 +6394,39 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K53" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="F53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6481,7 +6477,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6501,39 +6497,39 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K54" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="F54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6584,7 +6580,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6604,17 +6600,17 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>80</v>
@@ -6632,11 +6628,11 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6687,7 +6683,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6707,10 +6703,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6733,7 +6729,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -6786,7 +6782,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:32:36+00:00</t>
+    <t>2025-02-24T13:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:36:50+00:00</t>
+    <t>2025-03-04T16:07:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T13:18:22+00:00</t>
+    <t>2025-03-14T15:47:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>intendedRecipient</t>
+    <t>CDA - intendedRecipient</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1062,42 +1062,42 @@
   <dimension ref="A1:AK56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="83.35546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="83.35546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="71.4609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="71.4609375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="151.96875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="130.28515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="105.80859375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.6015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="90.7109375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="33.09375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-intended-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
